--- a/docs/pension_data_combined_2026-06-25.xlsx
+++ b/docs/pension_data_combined_2026-06-25.xlsx
@@ -1228,7 +1228,7 @@
         <v>1.1425</v>
       </c>
       <c r="D48" t="n">
-        <v>3977806.34</v>
+        <v>3980068.57</v>
       </c>
     </row>
     <row r="49">
@@ -1246,7 +1246,7 @@
         <v>2.1457</v>
       </c>
       <c r="D49" t="n">
-        <v>85811748.76000001</v>
+        <v>85811307.56999999</v>
       </c>
     </row>
     <row r="50">
@@ -1264,7 +1264,7 @@
         <v>2.1655</v>
       </c>
       <c r="D50" t="n">
-        <v>273785433.07</v>
+        <v>273808318.7</v>
       </c>
     </row>
     <row r="51">
@@ -1282,7 +1282,7 @@
         <v>2.1826</v>
       </c>
       <c r="D51" t="n">
-        <v>416066760.22</v>
+        <v>416068672.4</v>
       </c>
     </row>
     <row r="52">
@@ -1300,7 +1300,7 @@
         <v>2.1862</v>
       </c>
       <c r="D52" t="n">
-        <v>504838853.06</v>
+        <v>504795586.2</v>
       </c>
     </row>
     <row r="53">
@@ -1354,7 +1354,7 @@
         <v>1.2142</v>
       </c>
       <c r="D55" t="n">
-        <v>68424691.64</v>
+        <v>68412046.66</v>
       </c>
     </row>
   </sheetData>
